--- a/src/evaluation/ground_truth_report.xlsx
+++ b/src/evaluation/ground_truth_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>BERTScore F1</t>
+          <t>BLEU-1</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>BLEU-1</t>
+          <t>BLEU-2</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>BLEU-2</t>
+          <t>ROUGE-L</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>ROUGE-L</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Composite score</t>
         </is>
@@ -552,19 +547,16 @@
         <v>0.8013</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.0199</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0199</v>
+        <v>0.019</v>
       </c>
       <c r="H2" t="n">
-        <v>0.019</v>
+        <v>0.039</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0253</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5707</v>
       </c>
     </row>
     <row r="3">
@@ -593,19 +585,16 @@
         <v>0.7579</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.1002</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1002</v>
+        <v>0.0958</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0958</v>
+        <v>0.1706</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.5405</v>
+        <v>0.5747</v>
       </c>
     </row>
     <row r="4">
@@ -635,19 +624,16 @@
         <v>0.8343</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.0827</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0827</v>
+        <v>0.0702</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0702</v>
+        <v>0.126</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2857</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.6494</v>
+        <v>0.6175</v>
       </c>
     </row>
     <row r="5">
@@ -676,19 +662,16 @@
         <v>0.8436</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.0861</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0861</v>
+        <v>0.0823</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0823</v>
+        <v>0.1553</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.5991</v>
+        <v>0.6302</v>
       </c>
     </row>
     <row r="6">
@@ -718,19 +701,16 @@
         <v>0.8527</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.0839</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0839</v>
+        <v>0.0803</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0803</v>
+        <v>0.1478</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5217000000000001</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.7096</v>
+        <v>0.6348</v>
       </c>
     </row>
     <row r="7">
@@ -760,19 +740,16 @@
         <v>0.8677</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.1277</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2941</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.6731</v>
+        <v>0.6399</v>
       </c>
     </row>
     <row r="8">
@@ -811,19 +788,16 @@
         <v>0.7975</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.0353</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0353</v>
+        <v>0.0328</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0328</v>
+        <v>0.0653</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.5618</v>
+        <v>0.5749</v>
       </c>
     </row>
     <row r="9">
@@ -854,19 +828,16 @@
         <v>0.8206</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05</v>
+        <v>0.0475</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0475</v>
+        <v>0.0926</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1053</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.6005</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="10">
@@ -898,19 +869,16 @@
         <v>0.7913</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.0545</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0545</v>
+        <v>0.0529</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0529</v>
+        <v>0.1013</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.5594</v>
+        <v>0.5797</v>
       </c>
     </row>
     <row r="11">
@@ -940,19 +908,16 @@
         <v>0.7402</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.0712</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0712</v>
+        <v>0.0682</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0682</v>
+        <v>0.1268</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.5253</v>
+        <v>0.5506</v>
       </c>
     </row>
     <row r="12">
@@ -991,19 +956,16 @@
         <v>0.8164</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="G12" t="n">
-        <v>0.114</v>
+        <v>0.1037</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1037</v>
+        <v>0.1782</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.5829</v>
+        <v>0.6185</v>
       </c>
     </row>
     <row r="13">
@@ -1066,19 +1028,16 @@
         <v>0.7865</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="G13" t="n">
-        <v>0.042</v>
+        <v>0.0405</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0405</v>
+        <v>0.0771</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.5548</v>
+        <v>0.5702</v>
       </c>
     </row>
     <row r="14">
@@ -1107,19 +1066,16 @@
         <v>0.8431</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.6703</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6703</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.367</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.6572</v>
+        <v>0.7306</v>
       </c>
     </row>
     <row r="15">
@@ -1147,19 +1103,16 @@
         <v>0.795</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.1489</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1489</v>
+        <v>0.1429</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1429</v>
+        <v>0.2217</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.5714</v>
+        <v>0.6157</v>
       </c>
     </row>
     <row r="16">
@@ -1233,19 +1186,16 @@
         <v>0.8952</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.1208</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1208</v>
+        <v>0.11</v>
       </c>
       <c r="H16" t="n">
-        <v>0.11</v>
+        <v>0.1654</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.6387</v>
+        <v>0.6718</v>
       </c>
     </row>
     <row r="17">
@@ -1277,19 +1227,16 @@
         <v>0.751</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.0682</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0682</v>
+        <v>0.0663</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0663</v>
+        <v>0.1206</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.5325</v>
+        <v>0.5567</v>
       </c>
     </row>
     <row r="18">
@@ -1321,19 +1268,16 @@
         <v>0.7995</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.0452</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0452</v>
+        <v>0.0433</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0433</v>
+        <v>0.0847</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.5642</v>
+        <v>0.5810999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1364,19 +1308,16 @@
         <v>0.8258</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.1556</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.5875</v>
+        <v>0.6186</v>
       </c>
     </row>
     <row r="20">
@@ -1407,19 +1348,16 @@
         <v>0.8224</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.0711</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0711</v>
+        <v>0.0697</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0697</v>
+        <v>0.1289</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.5828</v>
+        <v>0.6086</v>
       </c>
     </row>
     <row r="21">
@@ -1447,19 +1385,16 @@
         <v>0.7669</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.1565</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1565</v>
+        <v>0.1397</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1397</v>
+        <v>0.2118</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.5525</v>
+        <v>0.5949</v>
       </c>
     </row>
     <row r="22">
@@ -1487,22 +1422,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9216</v>
+        <v>0.9217</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.452</v>
       </c>
       <c r="G22" t="n">
-        <v>0.452</v>
+        <v>0.45</v>
       </c>
       <c r="H22" t="n">
-        <v>0.45</v>
+        <v>0.6099</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5881999999999999</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8123</v>
       </c>
     </row>
     <row r="23">
@@ -1535,19 +1467,16 @@
         <v>0.8444</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.0926</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0926</v>
+        <v>0.0901</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0901</v>
+        <v>0.1511</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.6306</v>
       </c>
     </row>
     <row r="24">
@@ -1577,19 +1506,16 @@
         <v>0.8080000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.0764</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0764</v>
+        <v>0.0737</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0737</v>
+        <v>0.1355</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.5733</v>
+        <v>0.6002999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1621,19 +1547,16 @@
         <v>0.7947</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.0416</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0416</v>
+        <v>0.0408</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0408</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.5605</v>
+        <v>0.5764</v>
       </c>
     </row>
     <row r="26">
@@ -1676,19 +1599,16 @@
         <v>0.798</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.0338</v>
       </c>
       <c r="G26" t="n">
         <v>0.0338</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0338</v>
+        <v>0.0654</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5750999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1717,19 +1637,16 @@
         <v>0.8532999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.205</v>
       </c>
       <c r="G27" t="n">
-        <v>0.205</v>
+        <v>0.1905</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1905</v>
+        <v>0.263</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.6178</v>
+        <v>0.6704</v>
       </c>
     </row>
     <row r="28">
@@ -1768,19 +1685,16 @@
         <v>0.77</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.0759</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0759</v>
+        <v>0.064</v>
       </c>
       <c r="H28" t="n">
-        <v>0.064</v>
+        <v>0.1221</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.5466</v>
+        <v>0.571</v>
       </c>
     </row>
     <row r="29">
@@ -1807,19 +1721,16 @@
         <v>0.7659</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.2737</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2737</v>
+        <v>0.2241</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2241</v>
+        <v>0.2826</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.5635</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="30">
@@ -1847,19 +1758,16 @@
         <v>0.8184</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.0616</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0616</v>
+        <v>0.057</v>
       </c>
       <c r="H30" t="n">
-        <v>0.057</v>
+        <v>0.1094</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1053</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.6001</v>
+        <v>0.6009</v>
       </c>
     </row>
     <row r="31">
@@ -1889,19 +1797,16 @@
         <v>0.7957</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.6057</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6057</v>
+        <v>0.4371</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4371</v>
+        <v>0.3636</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.6176</v>
+        <v>0.6903</v>
       </c>
     </row>
     <row r="32">
@@ -1932,19 +1837,16 @@
         <v>0.8711</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.1127</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1127</v>
+        <v>0.1083</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1083</v>
+        <v>0.1772</v>
       </c>
       <c r="I32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.771</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="33">
@@ -1974,19 +1876,16 @@
         <v>0.852</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>0.699</v>
       </c>
       <c r="G33" t="n">
-        <v>0.699</v>
+        <v>0.5423</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5423</v>
+        <v>0.405</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.6663</v>
+        <v>0.7473</v>
       </c>
     </row>
     <row r="34">
@@ -2015,19 +1914,16 @@
         <v>0.8227</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.2159</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2159</v>
+        <v>0.1736</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1736</v>
+        <v>0.252</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.5975</v>
+        <v>0.6479</v>
       </c>
     </row>
     <row r="35">
@@ -2057,19 +1953,16 @@
         <v>0.8763</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.539</v>
       </c>
       <c r="G35" t="n">
-        <v>0.539</v>
+        <v>0.4406</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4406</v>
+        <v>0.4231</v>
       </c>
       <c r="I35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.7173</v>
+        <v>0.7519</v>
       </c>
     </row>
     <row r="36">
@@ -2100,19 +1993,16 @@
         <v>0.8853</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.3118</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3118</v>
+        <v>0.2881</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2881</v>
+        <v>0.4265</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1538</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.6817</v>
+        <v>0.7362</v>
       </c>
     </row>
     <row r="37">
@@ -2140,19 +2030,16 @@
         <v>0.7895</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>0.1713</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1713</v>
+        <v>0.1595</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1595</v>
+        <v>0.2393</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.5697</v>
+        <v>0.6176</v>
       </c>
     </row>
     <row r="38">
@@ -2182,19 +2069,16 @@
         <v>0.824</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>0.1123</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1123</v>
+        <v>0.1091</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1091</v>
+        <v>0.1829</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.588</v>
+        <v>0.6246</v>
       </c>
     </row>
     <row r="39">
@@ -2223,19 +2107,16 @@
         <v>0.8516</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>0.227</v>
       </c>
       <c r="G39" t="n">
-        <v>0.227</v>
+        <v>0.2145</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2145</v>
+        <v>0.2878</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.6188</v>
+        <v>0.6764</v>
       </c>
     </row>
     <row r="40">
@@ -2264,19 +2145,16 @@
         <v>0.8290999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>0.1657</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1657</v>
+        <v>0.1518</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1518</v>
+        <v>0.2412</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.597</v>
+        <v>0.6452</v>
       </c>
     </row>
     <row r="41">
@@ -2307,19 +2185,16 @@
         <v>0.7964</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>0.1346</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1346</v>
+        <v>0.12</v>
       </c>
       <c r="H41" t="n">
-        <v>0.12</v>
+        <v>0.194</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.571</v>
+        <v>0.6097</v>
       </c>
     </row>
     <row r="42">
@@ -2349,19 +2224,16 @@
         <v>0.838</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>0.2136</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2136</v>
+        <v>0.2032</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2032</v>
+        <v>0.2701</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.6079</v>
+        <v>0.662</v>
       </c>
     </row>
     <row r="43">
@@ -2391,19 +2263,16 @@
         <v>0.8976</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>0.4538</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4538</v>
+        <v>0.3756</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3756</v>
+        <v>0.4533</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.6737</v>
+        <v>0.7644</v>
       </c>
     </row>
     <row r="44">
@@ -2433,19 +2302,16 @@
         <v>0.8569</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>0.4513</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4513</v>
+        <v>0.3805</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3805</v>
+        <v>0.4103</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.6449</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="45">
@@ -2472,19 +2338,16 @@
         <v>0.7746</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>0.5563</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5563</v>
+        <v>0.425</v>
       </c>
       <c r="H45" t="n">
-        <v>0.425</v>
+        <v>0.3507</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.5979</v>
+        <v>0.668</v>
       </c>
     </row>
     <row r="46">
@@ -2514,19 +2377,16 @@
         <v>0.868</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>0.5349</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5349</v>
+        <v>0.4273</v>
       </c>
       <c r="H46" t="n">
-        <v>0.4273</v>
+        <v>0.3847</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.6611</v>
+        <v>0.738</v>
       </c>
     </row>
     <row r="47">
@@ -2554,19 +2414,16 @@
         <v>0.7961</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>0.2923</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2923</v>
+        <v>0.2431</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2431</v>
+        <v>0.3066</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1333</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.6131</v>
+        <v>0.6478</v>
       </c>
     </row>
     <row r="48">
@@ -2594,19 +2451,16 @@
         <v>0.7521</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>0.1411</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1411</v>
+        <v>0.1325</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1325</v>
+        <v>0.2107</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.5406</v>
+        <v>0.5827</v>
       </c>
     </row>
     <row r="49">
@@ -2635,19 +2489,16 @@
         <v>0.8633</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>0.0709</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0709</v>
+        <v>0.0687</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0687</v>
+        <v>0.1244</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.6363</v>
       </c>
     </row>
     <row r="50">
@@ -2677,19 +2528,16 @@
         <v>0.8501</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>0.3772</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3772</v>
+        <v>0.3304</v>
       </c>
       <c r="H50" t="n">
-        <v>0.3304</v>
+        <v>0.3893</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.6328</v>
+        <v>0.7106</v>
       </c>
     </row>
     <row r="51">
@@ -2718,19 +2566,16 @@
         <v>0.7788</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>0.1536</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1536</v>
+        <v>0.1412</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1412</v>
+        <v>0.2057</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.5605</v>
+        <v>0.6017</v>
       </c>
     </row>
   </sheetData>
